--- a/ExcelData/LocalizationTable.xlsx
+++ b/ExcelData/LocalizationTable.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\MFramework\ExcelData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7875D046-0BF0-4EDB-83A3-2F1A8A42B171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>编号</t>
   </si>
   <si>
+    <t>描述</t>
+  </si>
+  <si>
     <t>中文</t>
   </si>
   <si>
@@ -47,16 +44,25 @@
     <t>ID</t>
   </si>
   <si>
+    <t>Desc</t>
+  </si>
+  <si>
     <t>Chinese</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
+    <t>标题界面按钮</t>
   </si>
   <si>
     <t>开始</t>
@@ -71,82 +77,38 @@
     <t>Settings</t>
   </si>
   <si>
-    <t>语言</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
     <t>退出</t>
   </si>
   <si>
     <t>Quit</t>
   </si>
   <si>
-    <t>描述</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>none</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartBtn</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>物体名</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>GOName</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OptionsBtn</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>LanguageBtn</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExitBtn</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SoundBtn</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>菜单界面按钮</t>
+  </si>
+  <si>
+    <t>语言:中文</t>
+  </si>
+  <si>
+    <t>Language:English</t>
   </si>
   <si>
     <t>音量</t>
   </si>
   <si>
     <t>Sound</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>标题界面按钮</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>菜单界面按钮</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -162,47 +124,360 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -210,11 +485,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -222,174 +739,96 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -400,7 +839,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -428,40 +867,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -719,160 +1272,136 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="13.775" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.8833333333333" customWidth="1"/>
+    <col min="4" max="4" width="18.2166666666667" customWidth="1"/>
+    <col min="5" max="5" width="16.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelData/LocalizationTable.xlsx
+++ b/ExcelData/LocalizationTable.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\MFramework\ExcelData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA12391-36B0-48FF-B14F-A64A44FB2565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>编号</t>
   </si>
   <si>
+    <t>物体名</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -50,6 +47,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>GOName</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -65,7 +65,13 @@
     <t>none</t>
   </si>
   <si>
-    <t>标题界面按钮</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>MText</t>
   </si>
   <si>
     <t>开始</t>
@@ -74,92 +80,108 @@
     <t>Start</t>
   </si>
   <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>Settings</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>选项</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>退出</t>
   </si>
   <si>
-    <t>Quit</t>
-  </si>
-  <si>
-    <t>菜单界面按钮</t>
-  </si>
-  <si>
-    <t>语言:中文</t>
-  </si>
-  <si>
-    <t>Language:English</t>
-  </si>
-  <si>
-    <t>菜单界面按钮</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>音量:{开|关}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound:{On|Off}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>{我|#你}是{牛逼|#傻逼|无敌}的人</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>LanguageText</t>
   </si>
   <si>
     <r>
-      <t>{0}</t>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>是</t>
+      <t>中文</t>
+    </r>
+  </si>
+  <si>
+    <t>Language:English</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>SoundText</t>
+  </si>
+  <si>
+    <r>
+      <t>声音</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
-      <t>{1}</t>
+      <t>:{#</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>的人</t>
+      <t>开|关</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>你是傻逼的人  此时：pos[0]=你 pos[1]=傻逼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>傻逼---&gt;无敌  重新完整创建</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t>Sound:{#On|Off}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -168,52 +190,361 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -221,182 +552,347 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -407,7 +903,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -435,40 +931,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -726,23 +1336,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" customWidth="1"/>
-    <col min="2" max="2" width="52.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.14166666666667" customWidth="1"/>
+    <col min="2" max="2" width="12.35" customWidth="1"/>
+    <col min="3" max="3" width="9.14166666666667" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" ht="15" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,127 +1365,121 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" ht="15" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="3" ht="15" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
+      <c r="E6" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>12</v>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B14" s="6" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
         <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelData/LocalizationTable.xlsx
+++ b/ExcelData/LocalizationTable.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\MFramework\ExcelData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD6D9A4-2704-43BF-AA43-88C69A1D55C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>编号</t>
   </si>
@@ -53,12 +61,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>-1</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -87,14 +89,120 @@
   </si>
   <si>
     <t>SoundText</t>
+  </si>
+  <si>
+    <t>开始</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Settings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>退出</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语言:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中文</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Language:English</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>音量:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>{#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound:{#On|Off}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -103,6 +211,40 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -123,37 +265,368 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="12.3474102020264" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="5" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -170,7 +643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -187,7 +660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -204,7 +677,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" ht="15">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -212,10 +685,14 @@
         <v>14</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" ht="15">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -223,10 +700,14 @@
         <v>16</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" ht="15">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -234,10 +715,14 @@
         <v>18</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -245,10 +730,14 @@
         <v>20</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" ht="15">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -256,21 +745,15 @@
         <v>22</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <headerFooter/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ExcelData/LocalizationTable.xlsx
+++ b/ExcelData/LocalizationTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\MFramework\ExcelData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\___MYPROJECT___\UnityProject\MFramework\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD6D9A4-2704-43BF-AA43-88C69A1D55C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D3001E-ECA3-42B5-8761-0B723213BC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="19470" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -202,7 +202,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -619,14 +619,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="5" width="9.109375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -643,7 +645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -660,7 +662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -677,7 +679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15">
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -692,7 +694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15">
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -707,7 +709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15">
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -722,7 +724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15">
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -737,7 +739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15">
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
